--- a/reports/classeur_valorisation_cn.xlsx
+++ b/reports/classeur_valorisation_cn.xlsx
@@ -1451,7 +1451,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Actions diluées (millions)</t>
+          <t>Actions en circulation (millions)</t>
         </is>
       </c>
       <c r="B7" t="n">
